--- a/artfynd/A 60251-2021 artfynd.xlsx
+++ b/artfynd/A 60251-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60251-2021 artfynd.xlsx
+++ b/artfynd/A 60251-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97592344</v>
+        <v>132159</v>
       </c>
       <c r="B2" t="n">
-        <v>105123</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220103</v>
+        <v>340</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Dal nära Idrottsplatsen, Srm</t>
+          <t>Lilla Dal Dunker 500 m sv, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603098.2276344382</v>
+        <v>603015</v>
       </c>
       <c r="R2" t="n">
-        <v>6560860.325416985</v>
+        <v>6560772</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1978-07-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1978-07-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,71 +768,66 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>ruderatmark</t>
+          <t>Grandominerad 100-årig skog m tall o lövträd</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97592041</v>
+        <v>1156507</v>
       </c>
       <c r="B3" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219955</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lilla Dal nära Idrottsplatsen, Srm</t>
+          <t>Lilla Dal Dunker 500 m sv, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603098.2276344382</v>
+        <v>603015</v>
       </c>
       <c r="R3" t="n">
-        <v>6560860.325416985</v>
+        <v>6560772</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,27 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1978-07-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1978-07-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>litet bestånd</t>
+          <t>2008-09-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,21 +870,564 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>tallskog</t>
+          <t>Grandominerad 100-årig skog m tall o lövträd</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1739828</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lilla Dal Dunker 500 m sv, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>603015</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6560772</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2008-09-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2008-09-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Grandominerad 100-årig skog m tall o lövträd</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>97592041</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lilla Dal nära Idrottsplatsen, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>603098</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6560860</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1978-07-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1978-07-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>litet bestånd</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Hans Rydberg</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Hans Rydberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97592344</v>
+      </c>
+      <c r="B6" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lilla Dal nära Idrottsplatsen, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>603098</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6560860</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1978-07-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1978-07-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>ruderatmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3024414</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vilstadium</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lilla Dal Dunker 500 m sv, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>603015</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6560772</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2007-04-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2007-04-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3420986</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vilstadium</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lilla Dal Dunker 500 m sv, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>603015</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6560772</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2007-04-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2007-04-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60251-2021 artfynd.xlsx
+++ b/artfynd/A 60251-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132159</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1156507</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1739828</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97592041</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97592344</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3024414</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,8 +1463,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3420986</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>